--- a/results/log_pv_cap_fit/log_pv_cap_fit_baseline_estimates.xlsx
+++ b/results/log_pv_cap_fit/log_pv_cap_fit_baseline_estimates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,41 +462,11 @@
           <t>baseline-ML_ErrorFE-queen-Running ML_ErrorFE:queen for log_pv_cap_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>baseline-PooledOLS-inverse_distance-Running PooledOLS:inverse_distance for log_pv_cap_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>baseline-PooledOLS-k_nearest-Running PooledOLS:k_nearest for log_pv_cap_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>baseline-PooledOLS-queen-Running PooledOLS:queen for log_pv_cap_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>baseline-PanelRE-inverse_distance-Running PanelRE:inverse_distance for log_pv_cap_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>baseline-PanelRE-k_nearest-Running PanelRE:k_nearest for log_pv_cap_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>baseline-PanelRE-queen-Running PanelRE:queen for log_pv_cap_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,43 +512,13 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>0.325***</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-1.165***</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-1.165***</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-1.165***</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2.157***</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2.157***</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2.157***</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -624,43 +564,13 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>0.002*</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>-0.000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -706,126 +616,96 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>0.149***</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.297+</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.297+</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.297+</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-0.236***</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-0.236***</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>-0.236***</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W_log_income</t>
+          <t>Spatial term, ρ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.367**</t>
+          <t>0.902***</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.576***</t>
+          <t>0.746***</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.832***</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>0.619***</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.958***</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.809***</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.706***</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W_log_hholds</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>-0.055***</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>-0.007+</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>-0.008***</t>
-        </is>
-      </c>
+          <t>Spatial term, λ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.977***</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.909***</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.851***</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W_log_sunny_hours</t>
+          <t>W(Income)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.217***</t>
+          <t>0.367**</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.278***</t>
+          <t>0.576***</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.309***</t>
+          <t>0.832***</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -834,858 +714,320 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W_log_pv_cap_fit</t>
+          <t>W(Households)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.902***</t>
+          <t>-0.055***</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.746***</t>
+          <t>-0.007+</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.619***</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.958***</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0.809***</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.706***</t>
-        </is>
-      </c>
+          <t>-0.008***</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>W(Sunny hours)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.880</t>
+          <t>-0.217***</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.861</t>
+          <t>-0.278***</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.843</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.879</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.860</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.838</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.260</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.459</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.508</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.098</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0.098</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.098</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0.098</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0.098</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0.098</t>
-        </is>
-      </c>
+          <t>-0.309***</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>aic</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-9985.650</t>
+          <t>0.880</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-9539.186</t>
+          <t>0.861</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-9261.783</t>
+          <t>0.843</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-9966.910</t>
+          <t>0.879</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-9468.975</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-9125.878</t>
+          <t>0.838</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-9968.906</t>
+          <t>0.260</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-9358.781</t>
+          <t>0.459</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8904.557</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1533.275</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1533.275</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1533.275</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2870.244</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2870.244</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2870.244</t>
+          <t>0.508</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>schwarz</t>
+          <t>AIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-9946.183</t>
+          <t>-9985.650</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-9499.718</t>
+          <t>-9539.186</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-9222.316</t>
+          <t>-9261.783</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-9944.357</t>
+          <t>-9966.910</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-9446.422</t>
+          <t>-9468.975</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-9103.325</t>
+          <t>-9125.878</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9951.992</t>
+          <t>-9968.906</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-9341.866</t>
+          <t>-9358.781</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-8887.642</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1555.827</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1555.827</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1555.827</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2892.796</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2892.796</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2892.796</t>
+          <t>-8904.557</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>llr</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4999.825</t>
+          <t>-9946.183</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4776.593</t>
+          <t>-9499.718</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4637.892</t>
+          <t>-9222.316</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4987.455</t>
+          <t>-9944.357</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4738.487</t>
+          <t>-9446.422</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4566.939</t>
+          <t>-9103.325</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4987.453</t>
+          <t>-9951.992</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4682.390</t>
+          <t>-9341.866</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4455.278</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>-762.637</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-762.637</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>-762.637</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-1431.122</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>-1431.122</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>-1431.122</t>
+          <t>-8887.642</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>n_obs</t>
+          <t>Log-Likelihood</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4999.825</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4776.593</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4637.892</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4987.455</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4738.487</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4566.939</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4987.453</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4682.390</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2076</t>
+          <t>4455.278</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    67.065162   1      0.0
-1  LM Marginal Spatial (LM2)    19.413202   1      0.0
-2             LM Joint (LMJ)  4874.608388   2      0.0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    67.065162   1      0.0
-1  LM Marginal Spatial (LM2)     8.371570   1      0.0
-2             LM Joint (LMJ)  4567.819182   2      0.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    67.065162   1      0.0
-1  LM Marginal Spatial (LM2)     8.766631   1      0.0
-2             LM Joint (LMJ)  4574.589817   2      0.0</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial  170.058772  1     0.0
-1  Hausman Specification Test -141.113233  3     1.0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial   41.998821  1     0.0
-1  Hausman Specification Test -141.113233  3     1.0</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial   28.512162  1     0.0
-1  Hausman Specification Test -141.113233  3     1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0         log_income     0.062857  0.070192   0.895499   0.37052
-1         log_hholds     0.000521  0.001138   0.457582  0.647253
-2    log_sunny_hours     0.106005   0.03295    3.21713  0.001295
-3       W_log_income     0.367138  0.127785   2.873079  0.004065
-4       W_log_hholds    -0.055357  0.015831  -3.496781  0.000471
-5  W_log_sunny_hours    -0.216916  0.051976  -4.173356   0.00003
-6   W_log_pv_cap_fit      0.90247  0.024018  37.574257       0.0</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0         log_income     0.113146  0.071933   1.572921  0.115737
-1         log_hholds     0.000691  0.001222   0.565384  0.571812
-2    log_sunny_hours     0.096551  0.033532   2.879404  0.003984
-3       W_log_income     0.575545  0.089047   6.463373       0.0
-4       W_log_hholds    -0.006701  0.003612  -1.855544  0.063519
-5  W_log_sunny_hours    -0.277822  0.044376  -6.260702       0.0
-6   W_log_pv_cap_fit     0.746063  0.018809  39.665577       0.0</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0         log_income     0.154348  0.073333   2.104762  0.035312
-1         log_hholds     0.000667  0.001301   0.512208  0.608506
-2    log_sunny_hours     0.075135  0.034913   2.152051  0.031393
-3       W_log_income     0.831768  0.085683   9.707479       0.0
-4       W_log_hholds    -0.008068  0.002131  -3.786068  0.000153
-5  W_log_sunny_hours    -0.308629   0.04371  -7.060777       0.0
-6   W_log_pv_cap_fit     0.618734   0.02063  29.992007       0.0</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          var_names coefficients   std_err    zt_stat      prob
-0        log_income     0.083354  0.030636   2.720747  0.006513
-1        log_hholds     0.000695   0.00114   0.609782  0.542007
-2   log_sunny_hours      0.03238  0.022944   1.411277  0.158163
-3  W_log_pv_cap_fit      0.95757   0.01108  86.424262       0.0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          var_names coefficients   std_err    zt_stat      prob
-0        log_income      0.42689  0.037234  11.464999       0.0
-1        log_hholds     0.001256  0.001229     1.0218  0.306876
-2   log_sunny_hours    -0.009783  0.024049  -0.406802  0.684154
-3  W_log_pv_cap_fit     0.808745  0.014278  56.642678       0.0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          var_names coefficients   std_err    zt_stat      prob
-0        log_income     0.647566   0.04199  15.421813       0.0
-1        log_hholds      0.00121  0.001322   0.915676  0.359837
-2   log_sunny_hours    -0.030619  0.025855  -1.184267  0.236307
-3  W_log_pv_cap_fit     0.705937  0.016442  42.934628       0.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err     zt_stat      prob
-0       log_income     0.078768  0.070045    1.124543  0.260783
-1       log_hholds     0.000884  0.001136    0.778254   0.43642
-2  log_sunny_hours     0.106426  0.032991    3.225952  0.001256
-3           lambda       0.9772  0.006362  153.601664       0.0</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0       log_income     0.221556  0.069755   3.176196  0.001492
-1       log_hholds     0.001717  0.001162   1.477346  0.139583
-2  log_sunny_hours     0.131555  0.033682   3.905767  0.000094
-3           lambda     0.909165  0.008682  104.72334       0.0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0       log_income     0.325443  0.070845   4.593762  0.000004
-1       log_hholds     0.002353  0.001172   2.007592  0.044687
-2  log_sunny_hours     0.148664  0.035641   4.171143   0.00003
-3           lambda     0.851492  0.011768  72.357438       0.0</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     7.715696  0.532492  14.489786       0.0
-1       log_income    -1.164983  0.079305 -14.689953       0.0
-2       log_hholds      0.00215  0.009277   0.231788  0.816725
-3  log_sunny_hours     0.296743  0.167401   1.772652  0.076433</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     7.715696  0.532492  14.489786       0.0
-1       log_income    -1.164983  0.079305 -14.689953       0.0
-2       log_hholds      0.00215  0.009277   0.231788  0.816725
-3  log_sunny_hours     0.296743  0.167401   1.772652  0.076433</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     7.715696  0.532492  14.489786       0.0
-1       log_income    -1.164983  0.079305 -14.689953       0.0
-2       log_hholds      0.00215  0.009277   0.231788  0.816725
-3  log_sunny_hours     0.296743  0.167401   1.772652  0.076433</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.804879  0.207791 -23.123652       0.0
-1       log_income     2.156991  0.043422  49.675533       0.0
-2       log_hholds    -0.000144  0.002265   -0.06339  0.949456
-3  log_sunny_hours    -0.236034  0.044279  -5.330648       0.0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.804879  0.207791 -23.123652       0.0
-1       log_income     2.156991  0.043422  49.675533       0.0
-2       log_hholds    -0.000144  0.002265   -0.06339  0.949456
-3  log_sunny_hours    -0.236034  0.044279  -5.330648       0.0</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.804879  0.207791 -23.123652       0.0
-1       log_income     2.156991  0.043422  49.675533       0.0
-2       log_hholds    -0.000144  0.002265   -0.06339  0.949456
-3  log_sunny_hours    -0.236034  0.044279  -5.330648       0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>effects</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_inverse_distance  \
-log_income                                   4.408842   
-log_hholds                                  -0.562246   
-log_sunny_hours                             -1.137203   
-                 direct_ML_LagFE(SLX)_inverse_distance  \
-log_income                                    0.062857   
-log_hholds                                    0.000521   
-log_sunny_hours                               0.106005   
-                 indirect_ML_LagFE(SLX)_inverse_distance  
-log_income                                      4.345985  
-log_hholds                                     -0.562767  
-log_sunny_hours                                -1.243208  </t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_k_nearest  \
-log_income                            2.712051   
-log_hholds                           -0.023670   
-log_sunny_hours                      -0.713844   
-                 direct_ML_LagFE(SLX)_k_nearest  \
-log_income                             0.113146   
-log_hholds                             0.000691   
-log_sunny_hours                        0.096551   
-                 indirect_ML_LagFE(SLX)_k_nearest  
-log_income                               2.598906  
-log_hholds                              -0.024361  
-log_sunny_hours                         -0.810395  </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_queen  direct_ML_LagFE(SLX)_queen  \
-log_income                        2.586423                    0.154348   
-log_hholds                       -0.019412                    0.000667   
-log_sunny_hours                  -0.612417                    0.075135   
-                 indirect_ML_LagFE(SLX)_queen  
-log_income                           2.432075  
-log_hholds                          -0.020079  
-log_sunny_hours                     -0.687552  </t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_inverse_distance  \
-log_income                              1.964514   
-log_hholds                              0.016377   
-log_sunny_hours                         0.763148   
-                 direct_ML_LagFE_inverse_distance  \
-log_income                               0.083354   
-log_hholds                               0.000695   
-log_sunny_hours                          0.032380   
-                 indirect_ML_LagFE_inverse_distance  
-log_income                                 1.881160  
-log_hholds                                 0.015682  
-log_sunny_hours                            0.730767  </t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_k_nearest  direct_ML_LagFE_k_nearest  \
-log_income                       2.232043                   0.426890   
-log_hholds                       0.006565                   0.001256   
-log_sunny_hours                 -0.051153                  -0.009783   
-                 indirect_ML_LagFE_k_nearest  
-log_income                          1.805153  
-log_hholds                          0.005309  
-log_sunny_hours                    -0.041369  </t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_queen  direct_ML_LagFE_queen  \
-log_income                   2.202132               0.647566   
-log_hholds                   0.004116               0.001210   
-log_sunny_hours             -0.104124              -0.030619   
-                 indirect_ML_LagFE_queen  
-log_income                      1.554566  
-log_hholds                      0.002906  
-log_sunny_hours                -0.073505  </t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>lambda</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.977***</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.909***</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0.851***</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CONSTANT</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>7.716***</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>7.716***</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>7.716***</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-4.805***</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>-4.805***</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>-4.805***</t>
+          <t>N obs.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2076</t>
         </is>
       </c>
     </row>
